--- a/data/sxbet/ligas/Super Lig/trades.xlsx
+++ b/data/sxbet/ligas/Super Lig/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,1406 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1786656294</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2.31746</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>19.37</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1786648026</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>46.256716</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20.5068</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.4225</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1786647838</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>48.536805</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.1838</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>47.619048</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>47.595506</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>38.62999</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.8113</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>47.617861</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.6262</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2.954092</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>38.56999</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>47.617272</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>47.595506</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.1838</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>47.619048</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>0x11d9d432d7e4905e6b4dea8d4ffd97ac3083c3474849e0f633bdb38cfe98e826</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>46.36</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Super Lig</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>L19547664</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1786562478</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>1786732200</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>386.333333</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Super Lig/trades.xlsx
+++ b/data/sxbet/ligas/Super Lig/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
+          <t>0x96a718e5036292c04eda8a099fc1bfe4931d68c324d251bc9680ac7dfae26c0d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786656294</t>
+          <t>1786689484</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.31746</t>
+          <t>5.856354</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
+          <t>0xf3cb76ff35f741457025f079043311ce165e8adc8117fc4f8c39060ec00fe661</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +643,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -690,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786648026</t>
+          <t>1786689481</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>46.256716</t>
+          <t>6.430939</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
+          <t>0x1fa7a45b07827b4542762a5ca9e4abd3c2873b4e392b21dd381c3e57d08d393e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,31 +747,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.5068</t>
+          <t>5.17999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4225</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -802,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786647838</t>
+          <t>1786689393</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>48.536805</t>
+          <t>7.716931</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +843,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
+          <t>0xc3edc7001ce622a365c9f22b4b276dcb3fa943b0e7eb37fbd16932024736a22d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,22 +858,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3.5</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -914,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786689386</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>47.619048</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +955,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
+          <t>0x0277aa07615635c0510ca4bc4edd4cd895f315b7484bd81a0b21128a126bb337</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +970,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1026,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786689321</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>47.595506</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1067,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
+          <t>0x7da7c48dd0bea2c1605d7d5ab0f93d62934e030e84cc235f49d8042236775008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>38.62999</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1130,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786689255</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>47.617861</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,31 +1179,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+          <t>0x4a1609db924dd9c387fb8de9d105ed43baf4e58779d9aee234732e8e5e46518a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786647056</t>
+          <t>1786689190</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2.954092</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,31 +1291,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+          <t>0xe00b9517350e97755646b6ef93ecbd8afec44689bc621cbc505841d25f40dca6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>36.63999</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1338,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786647056</t>
+          <t>1786689123</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>47.584403</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,31 +1403,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+          <t>0xc0332b54f5b348e9daf479d415fa4737f402ed9d6df41f0bb64b200f5841519f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>38.56999</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1442,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786688930</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>47.617272</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,39 +1515,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+          <t>0x9813458723b7b9d5f1364b30b7946d7873cfa8da02d134dbe51c5aec9d8812b2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -3</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1554,7 +1562,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786687874</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>47.595506</t>
+          <t>8.923944</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+          <t>0xb9bb9d24faf4bfd886f280157336237743d1d597ba75c92bea7de28848f20fb8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1626,22 +1634,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3.5</t>
+          <t>Galatasaray SK -2.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1666,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786687241</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>47.619048</t>
+          <t>41.594306</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,28 +1731,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+          <t>0xdc40bf9bc16cf235537e7a69812970c27c7cdf0ec057a88e8f2cdf05e633faf2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>36.63999</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1770,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1800,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786685826</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1810,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>47.584403</t>
+          <t>48.959233</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,110 +1835,1406 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786656294</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2.31746</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>19.37</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786648026</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>46.256716</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20.5068</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.4225</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786647838</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>48.536805</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.1838</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>47.619048</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>47.595506</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>38.62999</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.8113</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>47.617861</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.6262</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2.954092</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>38.56999</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>47.617272</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>47.595506</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.1838</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>47.619048</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>0x11d9d432d7e4905e6b4dea8d4ffd97ac3083c3474849e0f633bdb38cfe98e826</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>46.36</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Super Lig</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>L19547664</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>1786562478</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>1786732200</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>386.333333</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Super Lig/trades.xlsx
+++ b/data/sxbet/ligas/Super Lig/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x96a718e5036292c04eda8a099fc1bfe4931d68c324d251bc9680ac7dfae26c0d</t>
+          <t>0x8eb95e07727eecff26d7e28ae9747c2ab7965a974c4dc6b1f0cf4f60fe3dcf67</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,12 +542,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786689484</t>
+          <t>1786708704</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>5.856354</t>
+          <t>20.100503</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +635,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf3cb76ff35f741457025f079043311ce165e8adc8117fc4f8c39060ec00fe661</t>
+          <t>0x6d827309844d7af10e2fc666df00cec34b49d3535b88c1ad2d294e86742d5401</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -659,7 +663,11 @@
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786689481</t>
+          <t>1786708324</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6.430939</t>
+          <t>11.033816</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x1fa7a45b07827b4542762a5ca9e4abd3c2873b4e392b21dd381c3e57d08d393e</t>
+          <t>0xdb1af061082debc5d686e26e1feeabf13afaf4c7367b6298b61ba4d7b393089d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,23 +755,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.17999</t>
+          <t>1.27497</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -786,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786689393</t>
+          <t>1786707724</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>7.716931</t>
+          <t>1.717131</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc3edc7001ce622a365c9f22b4b276dcb3fa943b0e7eb37fbd16932024736a22d</t>
+          <t>0x3a1405dad01a1e2e879928f27e93a0b5953a34d0ab186c27c1b344a9592c19af</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -858,39 +874,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>27.55999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -898,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786689386</t>
+          <t>1786707646</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>37.117832</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,27 +971,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0277aa07615635c0510ca4bc4edd4cd895f315b7484bd81a0b21128a126bb337</t>
+          <t>0xcaace36699e174f73e4672a10507967b8a93347b2a58f4ffdd1085b144145abc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -983,26 +995,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1040,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786689321</t>
+          <t>1786707458</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>3.846154</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,12 +1075,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7da7c48dd0bea2c1605d7d5ab0f93d62934e030e84cc235f49d8042236775008</t>
+          <t>0x845eed293c0a679a4d7f44f97bfe24dc6873d8c15ecea6311e6f943f82806c2a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1082,12 +1090,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1097,24 +1105,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1122,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786689255</t>
+          <t>1786707147</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>151.240876</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,12 +1187,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4a1609db924dd9c387fb8de9d105ed43baf4e58779d9aee234732e8e5e46518a</t>
+          <t>0x773ca279dd1fcdfd95641d3e865ac1c15cfaf639cb57dcd1a5ce2b159a79d5c9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,39 +1202,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>27.29998</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786689190</t>
+          <t>1786707081</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>36.76765</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,27 +1299,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe00b9517350e97755646b6ef93ecbd8afec44689bc621cbc505841d25f40dca6</t>
+          <t>0x7915c5da57ffdd5446ae88ee7510bd59159ace42a0d790506fe27eeccdfdd8e2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>166.89</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1319,26 +1323,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786689123</t>
+          <t>1786706610</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>641.884615</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,54 +1403,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc0332b54f5b348e9daf479d415fa4737f402ed9d6df41f0bb64b200f5841519f</t>
+          <t>0x0a8fffbc18f527c688873f2f70c21af596b8a54395ec941e4feb87f4e916c50f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1458,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786688930</t>
+          <t>1786706610</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>49.326829</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x9813458723b7b9d5f1364b30b7946d7873cfa8da02d134dbe51c5aec9d8812b2</t>
+          <t>0xe495787704c21d9862422d18967d34d2427d09b118c7153251d21f8a358df4e3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1523,23 +1515,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>98.77998</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786687874</t>
+          <t>1786706354</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>8.923944</t>
+          <t>130.834411</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb9bb9d24faf4bfd886f280157336237743d1d597ba75c92bea7de28848f20fb8</t>
+          <t>0x2f1937327bedbf2e7c212ccf58443b354ccd9877b2268e90e7e7db999d0c5634</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>6.32999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Galatasaray SK -2.5</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786687241</t>
+          <t>1786705734</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>41.594306</t>
+          <t>8.384093</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xdc40bf9bc16cf235537e7a69812970c27c7cdf0ec057a88e8f2cdf05e633faf2</t>
+          <t>0x8c40f4ea25a8d84fec1a9f2051d284621eb317f39ef576e6259f3d3465e01764</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1739,23 +1739,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>13.47999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1778,7 +1786,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786685826</t>
+          <t>1786705716</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.959233</t>
+          <t>17.854291</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
+          <t>0x0277dd0aebe5d8c7a8c9d9213d27aeb8863ee0b6dd6f25c9bc5c6cb8f8576da5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1843,23 +1851,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>98.97998</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1882,7 +1898,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786656294</t>
+          <t>1786705696</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.31746</t>
+          <t>131.099311</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,7 +1955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
+          <t>0x46b66c2899b85f503cccc5f67de585ac56c4acbda40d70960ffad512c8e056e9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1947,31 +1963,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>581.29412</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.915</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1994,7 +2002,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2024,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786648026</t>
+          <t>1786704867</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>46.256716</t>
+          <t>635.29412</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,7 +2059,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
+          <t>0x4294e00d7858123ad3b26cdb24ecc9a518c262a27fdb5040280e0c1e04c58677</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2059,31 +2067,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20.5068</t>
+          <t>602.81998</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4225</t>
+          <t>1.915</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786647838</t>
+          <t>1786704864</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.536805</t>
+          <t>658.81965</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,39 +2163,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
+          <t>0x4cf922d1e2d6269e67d6a514a4515188832fe859e91505d33649905388468d4f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>9.08999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2218,7 +2210,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2248,7 +2240,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786704852</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2258,7 +2250,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>47.619048</t>
+          <t>14.720632</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,12 +2267,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
+          <t>0x4d90e057d93cfc68db9ab18a085695bf869d7741bae368bdf2dbd877a68c2e20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2290,22 +2282,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2330,7 +2322,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2360,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786704038</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2370,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>47.595506</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,31 +2379,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
+          <t>0x5c7c7a69c35b22274ba0ee9ba3c275387e27cf9fae03a224b6537c798684b62e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>38.62999</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786703866</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>47.617861</t>
+          <t>112.848485</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+          <t>0x948dae997d9eccf400ee187c8ba958553204eae0142fe7a03cfae8cd6620e88f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2499,23 +2499,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>16.87999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.6887</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2538,7 +2546,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2568,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786647056</t>
+          <t>1786703243</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2578,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.954092</t>
+          <t>24.508152</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,28 +2603,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+          <t>0x14663cbc9f1993a9a1da764fd8ce40f9e6844722ad5feb3ac8ead29430186a11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>36.63999</t>
+          <t>75.05993</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2642,7 +2650,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2672,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786647056</t>
+          <t>1786702892</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>47.584403</t>
+          <t>81.58688</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,28 +2707,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+          <t>0xa1aab820d38249671bcf7e90f5586cda87617cdde2ee0be038153fc5954cdf7c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>38.56999</t>
+          <t>2.42993</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.9225</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2746,7 +2754,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2776,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786702195</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2786,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>47.617272</t>
+          <t>2.63407</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2803,12 +2811,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+          <t>0x600540942837eb33d421c900b7288a86c980a0b346f74dc131b7cdaa2dd6a496</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2818,22 +2826,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>8.58999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (2.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Genclerbirligi Sk +2.5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2843,27 +2851,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
+          <t>Genclerbirligi Sk vs Fenerbahçe</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Galatasaray SK</t>
+          <t>Genclerbirligi Sk</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0xa72b64b0ca933e5c6954ea5a6c80db4ec664dc64836b150cc73917145232017c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19547664</t>
+          <t>L19547685</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2888,17 +2896,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786700733</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786732200</t>
+          <t>1786818600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>47.595506</t>
+          <t>11.155831</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,39 +2923,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+          <t>0x94d8e5004e7176f2726a9cc2be60d8e8fe8c164fafefddb52d96b40e5906351b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>10.39932</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786697405</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>47.619048</t>
+          <t>48.089341</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,28 +3027,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+          <t>0x057dfb059d29bb8e6462d635b019e406205008ed333601856f3a4f218c6e771a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>36.63999</t>
+          <t>10.39932</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786697375</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>47.584403</t>
+          <t>48.089341</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,110 +3131,3886 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>0x6427f3d101c0e917aac28af7ae32d70fd3726361b8179434942b0d430ef7462e</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10.39932</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786697304</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>48.089341</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x911930dbac03eadd0379cbbe8ce10fe735e42e19c463219a6faa55e601aeb785</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786697101</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>17.433526</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xaac60d693bf0fa6ec90126590d2cd2187f392b62165508184f545018e85eb9c3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>49.99999</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.8588</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786695468</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>58.224151</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xb6078a9dbff76d9a3d0fd7dfc6fa4e942f2e57ee6fed05cbe866739451772a61</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>49.99999</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.8588</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786695402</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>58.224151</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0xd7d25e989c7c1bd73d8577425cd04cb6e99a4d9ea63e81d66a1cb585735b1074</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>49.99999</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.8588</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786695334</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>58.224151</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x153e5d73875db805ab5926c57372cc9323e0210ac7d4b7771cb0a4d95b566bd4</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>49.99999</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.8588</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786695268</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>58.224151</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xe10683ef299398b0f5aa0bf3e8b236543904b1a2f82516e2445529aa80612887</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>49.99999</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.8588</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786695203</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>58.224151</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x484b9ddb00f67185222c5271ad11dc2e37e0c64fe540a5d49ad83c64a11b8b9b</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.7625</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Torku Konyaspor vs Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Torku Konyaspor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x0bba83fa89f6167caadeccbb2b3930657f0a248835be4ce38ba9a0e9ae3dbb78</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19547688</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786692830</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786809600</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>65.57377</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x4a744a7164e08e94c9d15a1a5264ddd58945124df502dfc3b015e5af160a4432</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>13.79998</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786691914</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>17.692282</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0xadae1178f7a2de1bd568cf92b516d13b8fb88e70b856c02eb77c9e0b06e5b264</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>24.24999</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786691887</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>31.089731</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x059b37e47835b5b6655b7816df8fe7ad06a8d6b06ae81642936f5913e3911b0e</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.5562</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1.5</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786691585</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>8.988764</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x96a718e5036292c04eda8a099fc1bfe4931d68c324d251bc9680ac7dfae26c0d</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.4525</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786689484</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>5.856354</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xf3cb76ff35f741457025f079043311ce165e8adc8117fc4f8c39060ec00fe661</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.4525</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786689481</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>6.430939</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x1fa7a45b07827b4542762a5ca9e4abd3c2873b4e392b21dd381c3e57d08d393e</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5.17999</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.6713</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786689393</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>7.716931</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0xc3edc7001ce622a365c9f22b4b276dcb3fa943b0e7eb37fbd16932024736a22d</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>49.99998</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.7937</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786689386</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>62.992101</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x0277aa07615635c0510ca4bc4edd4cd895f315b7484bd81a0b21128a126bb337</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>49.99998</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.7937</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786689321</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>62.992101</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x7da7c48dd0bea2c1605d7d5ab0f93d62934e030e84cc235f49d8042236775008</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>49.99998</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.7937</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786689255</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>62.992101</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x4a1609db924dd9c387fb8de9d105ed43baf4e58779d9aee234732e8e5e46518a</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>49.99998</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.7937</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786689190</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>62.992101</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xe00b9517350e97755646b6ef93ecbd8afec44689bc621cbc505841d25f40dca6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>49.99998</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.7937</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786689123</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>62.992101</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0xc0332b54f5b348e9daf479d415fa4737f402ed9d6df41f0bb64b200f5841519f</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>49.99998</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.7937</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786688930</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>62.992101</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x9813458723b7b9d5f1364b30b7946d7873cfa8da02d134dbe51c5aec9d8812b2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.4438</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786687874</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>8.923944</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xb9bb9d24faf4bfd886f280157336237743d1d597ba75c92bea7de28848f20fb8</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>14.61</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.3513</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -2.5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786687241</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>41.594306</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0xdc40bf9bc16cf235537e7a69812970c27c7cdf0ec057a88e8f2cdf05e633faf2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>25.52</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.5212</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786685826</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>48.959233</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786656294</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2.31746</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>19.37</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786648026</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>46.256716</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20.5068</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.4225</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1786647838</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>48.536805</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.1838</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3.5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>47.619048</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>47.595506</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>38.62999</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.8113</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1786647057</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>47.617861</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.6262</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2.954092</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>38.56999</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>47.617272</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>47.595506</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.1838</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3.5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>47.619048</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>0x11d9d432d7e4905e6b4dea8d4ffd97ac3083c3474849e0f633bdb38cfe98e826</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>46.36</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Super Lig</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>L19547664</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>1786562478</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>1786732200</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>386.333333</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Super Lig/trades.xlsx
+++ b/data/sxbet/ligas/Super Lig/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8eb95e07727eecff26d7e28ae9747c2ab7965a974c4dc6b1f0cf4f60fe3dcf67</t>
+          <t>0xd4e6c403ea408b2339c0602c38d8d658ec27335338ae119d72db90402419ab7f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,23 +539,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.49949</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.1738</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786708704</t>
+          <t>1786711291</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20.100503</t>
+          <t>20.14095</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x6d827309844d7af10e2fc666df00cec34b49d3535b88c1ad2d294e86742d5401</t>
+          <t>0xb11371348313ba14af90748e92e8584e7206b88a586c8c456c008804fe3d92e2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5175</t>
+          <t>1.1738</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galatasaray SK -1.5</t>
+          <t>Galatasaray SK -3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786708324</t>
+          <t>1786711231</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11.033816</t>
+          <t>27.798561</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xdb1af061082debc5d686e26e1feeabf13afaf4c7367b6298b61ba4d7b393089d</t>
+          <t>0xa89cf31f8f686a1eb3d2d3b9e5dc11864cee90f422fb1e645205110d3f063f9e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -762,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.27497</t>
+          <t>4.83999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galatasaray SK -0.5</t>
+          <t>Galatasaray SK -1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786707724</t>
+          <t>1786710007</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.717131</t>
+          <t>7.27818</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3a1405dad01a1e2e879928f27e93a0b5953a34d0ab186c27c1b344a9592c19af</t>
+          <t>0xee3ae1e73db70bebda3eed568a596a69fc4861c78488eb47519907204bd91476</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27.55999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galatasaray SK -0.5</t>
+          <t>Galatasaray SK -1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786707646</t>
+          <t>1786710005</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37.117832</t>
+          <t>15.037594</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,31 +979,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xcaace36699e174f73e4672a10507967b8a93347b2a58f4ffdd1085b144145abc</t>
+          <t>0x27e9f22b3d6dc53e4afcb141880f34ad08460246598c5e33ddc37551b5a494fb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13.13999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1018,7 +1034,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786707458</t>
+          <t>1786709961</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.846154</t>
+          <t>19.759383</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1091,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x845eed293c0a679a4d7f44f97bfe24dc6873d8c15ecea6311e6f943f82806c2a</t>
+          <t>0x14d550541329b80b032170bb8cce7aeb98cd14feb66a15d56a7957278fc7559f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1090,22 +1106,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Galatasaray SK -1.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1130,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786707147</t>
+          <t>1786709961</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>151.240876</t>
+          <t>38.086957</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,7 +1203,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x773ca279dd1fcdfd95641d3e865ac1c15cfaf639cb57dcd1a5ce2b159a79d5c9</t>
+          <t>0x8eb95e07727eecff26d7e28ae9747c2ab7965a974c4dc6b1f0cf4f60fe3dcf67</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1195,31 +1211,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27.29998</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1242,7 +1250,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786707081</t>
+          <t>1786708704</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36.76765</t>
+          <t>20.100503</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,31 +1307,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x7915c5da57ffdd5446ae88ee7510bd59159ace42a0d790506fe27eeccdfdd8e2</t>
+          <t>0x6d827309844d7af10e2fc666df00cec34b49d3535b88c1ad2d294e86742d5401</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>166.89</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1346,7 +1362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786706610</t>
+          <t>1786708324</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>641.884615</t>
+          <t>11.033816</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1419,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x0a8fffbc18f527c688873f2f70c21af596b8a54395ec941e4feb87f4e916c50f</t>
+          <t>0xdb1af061082debc5d686e26e1feeabf13afaf4c7367b6298b61ba4d7b393089d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1411,15 +1427,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>1.27497</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1427,7 +1447,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1480,7 +1504,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786706610</t>
+          <t>1786707724</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1514,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>49.326829</t>
+          <t>1.717131</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1531,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xe495787704c21d9862422d18967d34d2427d09b118c7153251d21f8a358df4e3</t>
+          <t>0x3a1405dad01a1e2e879928f27e93a0b5953a34d0ab186c27c1b344a9592c19af</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1522,39 +1546,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>98.77998</t>
+          <t>27.55999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1562,7 +1586,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1616,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786706354</t>
+          <t>1786707646</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1626,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>130.834411</t>
+          <t>37.117832</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,27 +1643,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x2f1937327bedbf2e7c212ccf58443b354ccd9877b2268e90e7e7db999d0c5634</t>
+          <t>0xcaace36699e174f73e4672a10507967b8a93347b2a58f4ffdd1085b144145abc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.32999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1647,26 +1667,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1704,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786705734</t>
+          <t>1786707458</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>8.384093</t>
+          <t>3.846154</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1747,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x8c40f4ea25a8d84fec1a9f2051d284621eb317f39ef576e6259f3d3465e01764</t>
+          <t>0x845eed293c0a679a4d7f44f97bfe24dc6873d8c15ecea6311e6f943f82806c2a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,12 +1762,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13.47999</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1761,24 +1777,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1786,7 +1802,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1832,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786705716</t>
+          <t>1786707147</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1842,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17.854291</t>
+          <t>151.240876</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,7 +1859,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x0277dd0aebe5d8c7a8c9d9213d27aeb8863ee0b6dd6f25c9bc5c6cb8f8576da5</t>
+          <t>0x773ca279dd1fcdfd95641d3e865ac1c15cfaf639cb57dcd1a5ce2b159a79d5c9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1858,39 +1874,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>98.97998</t>
+          <t>27.29998</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -1898,7 +1914,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1928,7 +1944,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786705696</t>
+          <t>1786707081</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1954,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>131.099311</t>
+          <t>36.76765</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,7 +1971,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x46b66c2899b85f503cccc5f67de585ac56c4acbda40d70960ffad512c8e056e9</t>
+          <t>0x7915c5da57ffdd5446ae88ee7510bd59159ace42a0d790506fe27eeccdfdd8e2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1966,12 +1982,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>581.29412</t>
+          <t>166.89</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2002,7 +2018,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2032,7 +2048,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786704867</t>
+          <t>1786706610</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2058,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>635.29412</t>
+          <t>641.884615</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,7 +2075,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x4294e00d7858123ad3b26cdb24ecc9a518c262a27fdb5040280e0c1e04c58677</t>
+          <t>0x0a8fffbc18f527c688873f2f70c21af596b8a54395ec941e4feb87f4e916c50f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2070,17 +2086,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>602.81998</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2106,7 +2122,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2136,7 +2152,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786704864</t>
+          <t>1786706610</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2146,7 +2162,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>658.81965</t>
+          <t>49.326829</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,7 +2179,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x4cf922d1e2d6269e67d6a514a4515188832fe859e91505d33649905388468d4f</t>
+          <t>0xe495787704c21d9862422d18967d34d2427d09b118c7153251d21f8a358df4e3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2171,23 +2187,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.08999</t>
+          <t>98.77998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2210,7 +2234,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2240,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786704852</t>
+          <t>1786706354</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2250,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>14.720632</t>
+          <t>130.834411</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,7 +2291,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x4d90e057d93cfc68db9ab18a085695bf869d7741bae368bdf2dbd877a68c2e20</t>
+          <t>0x2f1937327bedbf2e7c212ccf58443b354ccd9877b2268e90e7e7db999d0c5634</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2282,12 +2306,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>6.32999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2297,7 +2321,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2322,7 +2346,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2352,7 +2376,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786704038</t>
+          <t>1786705734</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2362,7 +2386,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>8.384093</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,7 +2403,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5c7c7a69c35b22274ba0ee9ba3c275387e27cf9fae03a224b6537c798684b62e</t>
+          <t>0x8c40f4ea25a8d84fec1a9f2051d284621eb317f39ef576e6259f3d3465e01764</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2394,12 +2418,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>13.47999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2409,7 +2433,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2434,7 +2458,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2464,7 +2488,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786703866</t>
+          <t>1786705716</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2474,7 +2498,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>112.848485</t>
+          <t>17.854291</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,7 +2515,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x948dae997d9eccf400ee187c8ba958553204eae0142fe7a03cfae8cd6620e88f</t>
+          <t>0x0277dd0aebe5d8c7a8c9d9213d27aeb8863ee0b6dd6f25c9bc5c6cb8f8576da5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2506,22 +2530,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.87999</t>
+          <t>98.97998</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6887</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Galatasaray SK -1</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2546,7 +2570,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2576,7 +2600,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786703243</t>
+          <t>1786705696</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2586,7 +2610,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>24.508152</t>
+          <t>131.099311</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,7 +2627,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x14663cbc9f1993a9a1da764fd8ce40f9e6844722ad5feb3ac8ead29430186a11</t>
+          <t>0x46b66c2899b85f503cccc5f67de585ac56c4acbda40d70960ffad512c8e056e9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2614,12 +2638,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>75.05993</t>
+          <t>581.29412</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.915</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2680,7 +2704,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786702892</t>
+          <t>1786704867</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2690,7 +2714,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>81.58688</t>
+          <t>635.29412</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,7 +2731,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xa1aab820d38249671bcf7e90f5586cda87617cdde2ee0be038153fc5954cdf7c</t>
+          <t>0x4294e00d7858123ad3b26cdb24ecc9a518c262a27fdb5040280e0c1e04c58677</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2718,12 +2742,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.42993</t>
+          <t>602.81998</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.9225</t>
+          <t>1.915</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2784,7 +2808,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786702195</t>
+          <t>1786704864</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2818,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.63407</t>
+          <t>658.81965</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,39 +2835,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x600540942837eb33d421c900b7288a86c980a0b346f74dc131b7cdaa2dd6a496</t>
+          <t>0x4cf922d1e2d6269e67d6a514a4515188832fe859e91505d33649905388468d4f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.58999</t>
+          <t>9.08999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (2.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Genclerbirligi Sk +2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2851,27 +2867,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Genclerbirligi Sk vs Fenerbahçe</t>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Genclerbirligi Sk</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xa72b64b0ca933e5c6954ea5a6c80db4ec664dc64836b150cc73917145232017c</t>
+          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19547685</t>
+          <t>L19547664</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2896,17 +2912,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786700733</t>
+          <t>1786704852</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786818600</t>
+          <t>1786732200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>11.155831</t>
+          <t>14.720632</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,7 +2939,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x94d8e5004e7176f2726a9cc2be60d8e8fe8c164fafefddb52d96b40e5906351b</t>
+          <t>0x4d90e057d93cfc68db9ab18a085695bf869d7741bae368bdf2dbd877a68c2e20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2931,23 +2947,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.39932</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2970,7 +2994,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3000,7 +3024,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786697405</t>
+          <t>1786704038</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3034,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>48.089341</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,7 +3051,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x057dfb059d29bb8e6462d635b019e406205008ed333601856f3a4f218c6e771a</t>
+          <t>0x5c7c7a69c35b22274ba0ee9ba3c275387e27cf9fae03a224b6537c798684b62e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3035,23 +3059,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.39932</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -3074,7 +3106,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3104,7 +3136,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786697375</t>
+          <t>1786703866</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3114,7 +3146,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.089341</t>
+          <t>112.848485</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,7 +3163,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x6427f3d101c0e917aac28af7ae32d70fd3726361b8179434942b0d430ef7462e</t>
+          <t>0x948dae997d9eccf400ee187c8ba958553204eae0142fe7a03cfae8cd6620e88f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3139,23 +3171,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.39932</t>
+          <t>16.87999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.6887</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -3178,7 +3218,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3208,7 +3248,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786697304</t>
+          <t>1786703243</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3258,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>48.089341</t>
+          <t>24.508152</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,7 +3275,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x911930dbac03eadd0379cbbe8ce10fe735e42e19c463219a6faa55e601aeb785</t>
+          <t>0x14663cbc9f1993a9a1da764fd8ce40f9e6844722ad5feb3ac8ead29430186a11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3246,17 +3286,17 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>75.05993</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3282,7 +3322,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3312,7 +3352,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786697101</t>
+          <t>1786702892</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3322,7 +3362,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>17.433526</t>
+          <t>81.58688</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,23 +3379,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xaac60d693bf0fa6ec90126590d2cd2187f392b62165508184f545018e85eb9c3</t>
+          <t>0xa1aab820d38249671bcf7e90f5586cda87617cdde2ee0be038153fc5954cdf7c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>2.42993</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.9225</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3386,7 +3426,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3416,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786695468</t>
+          <t>1786702195</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3426,7 +3466,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>2.63407</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,31 +3483,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xb6078a9dbff76d9a3d0fd7dfc6fa4e942f2e57ee6fed05cbe866739451772a61</t>
+          <t>0x600540942837eb33d421c900b7288a86c980a0b346f74dc131b7cdaa2dd6a496</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>8.58999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Asian Handicap (2.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Genclerbirligi Sk +2.5</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -3475,27 +3523,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
+          <t>Genclerbirligi Sk vs Fenerbahçe</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Galatasaray SK</t>
+          <t>Genclerbirligi Sk</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xa72b64b0ca933e5c6954ea5a6c80db4ec664dc64836b150cc73917145232017c</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19547664</t>
+          <t>L19547685</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3520,17 +3568,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786695402</t>
+          <t>1786700733</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786732200</t>
+          <t>1786818600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>11.155831</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,28 +3595,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xd7d25e989c7c1bd73d8577425cd04cb6e99a4d9ea63e81d66a1cb585735b1074</t>
+          <t>0x94d8e5004e7176f2726a9cc2be60d8e8fe8c164fafefddb52d96b40e5906351b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>10.39932</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3594,7 +3642,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3624,7 +3672,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786695334</t>
+          <t>1786697405</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3634,7 +3682,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>48.089341</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3651,28 +3699,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x153e5d73875db805ab5926c57372cc9323e0210ac7d4b7771cb0a4d95b566bd4</t>
+          <t>0x057dfb059d29bb8e6462d635b019e406205008ed333601856f3a4f218c6e771a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>10.39932</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3698,7 +3746,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3728,7 +3776,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786695268</t>
+          <t>1786697375</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3738,7 +3786,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>48.089341</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,28 +3803,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe10683ef299398b0f5aa0bf3e8b236543904b1a2f82516e2445529aa80612887</t>
+          <t>0x6427f3d101c0e917aac28af7ae32d70fd3726361b8179434942b0d430ef7462e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>10.39932</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3802,7 +3850,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3832,7 +3880,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786695203</t>
+          <t>1786697304</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3842,7 +3890,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>48.089341</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3859,39 +3907,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x484b9ddb00f67185222c5271ad11dc2e37e0c64fe540a5d49ad83c64a11b8b9b</t>
+          <t>0x911930dbac03eadd0379cbbe8ce10fe735e42e19c463219a6faa55e601aeb785</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.7625</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -3899,27 +3939,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Torku Konyaspor vs Caykur Rizespor</t>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Torku Konyaspor</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Caykur Rizespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x0bba83fa89f6167caadeccbb2b3930657f0a248835be4ce38ba9a0e9ae3dbb78</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19547688</t>
+          <t>L19547664</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3944,17 +3984,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786692830</t>
+          <t>1786697101</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786809600</t>
+          <t>1786732200</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>65.57377</t>
+          <t>17.433526</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3971,39 +4011,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x4a744a7164e08e94c9d15a1a5264ddd58945124df502dfc3b015e5af160a4432</t>
+          <t>0xaac60d693bf0fa6ec90126590d2cd2187f392b62165508184f545018e85eb9c3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13.79998</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4026,7 +4058,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4056,7 +4088,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786691914</t>
+          <t>1786695468</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4066,7 +4098,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17.692282</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,39 +4115,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xadae1178f7a2de1bd568cf92b516d13b8fb88e70b856c02eb77c9e0b06e5b264</t>
+          <t>0xb6078a9dbff76d9a3d0fd7dfc6fa4e942f2e57ee6fed05cbe866739451772a61</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>24.24999</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4138,7 +4162,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4168,7 +4192,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786691887</t>
+          <t>1786695402</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4178,7 +4202,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>31.089731</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,39 +4219,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x059b37e47835b5b6655b7816df8fe7ad06a8d6b06ae81642936f5913e3911b0e</t>
+          <t>0xd7d25e989c7c1bd73d8577425cd04cb6e99a4d9ea63e81d66a1cb585735b1074</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4250,7 +4266,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4280,7 +4296,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786691585</t>
+          <t>1786695334</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4290,7 +4306,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,28 +4323,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x96a718e5036292c04eda8a099fc1bfe4931d68c324d251bc9680ac7dfae26c0d</t>
+          <t>0x153e5d73875db805ab5926c57372cc9323e0210ac7d4b7771cb0a4d95b566bd4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4354,7 +4370,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4384,7 +4400,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786689484</t>
+          <t>1786695268</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4394,7 +4410,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5.856354</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,28 +4427,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xf3cb76ff35f741457025f079043311ce165e8adc8117fc4f8c39060ec00fe661</t>
+          <t>0xe10683ef299398b0f5aa0bf3e8b236543904b1a2f82516e2445529aa80612887</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4458,7 +4474,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4488,7 +4504,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786689481</t>
+          <t>1786695203</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4498,7 +4514,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>6.430939</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,31 +4531,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x1fa7a45b07827b4542762a5ca9e4abd3c2873b4e392b21dd381c3e57d08d393e</t>
+          <t>0x484b9ddb00f67185222c5271ad11dc2e37e0c64fe540a5d49ad83c64a11b8b9b</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5.17999</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.7625</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4547,27 +4571,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
+          <t>Torku Konyaspor vs Caykur Rizespor</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Galatasaray SK</t>
+          <t>Torku Konyaspor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Caykur Rizespor</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x0bba83fa89f6167caadeccbb2b3930657f0a248835be4ce38ba9a0e9ae3dbb78</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19547664</t>
+          <t>L19547688</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4592,17 +4616,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786689393</t>
+          <t>1786692830</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786732200</t>
+          <t>1786809600</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>7.716931</t>
+          <t>65.57377</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,12 +4643,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xc3edc7001ce622a365c9f22b4b276dcb3fa943b0e7eb37fbd16932024736a22d</t>
+          <t>0x4a744a7164e08e94c9d15a1a5264ddd58945124df502dfc3b015e5af160a4432</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4634,39 +4658,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>13.79998</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -4674,7 +4698,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4704,7 +4728,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786689386</t>
+          <t>1786691914</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4714,7 +4738,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>17.692282</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,12 +4755,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x0277aa07615635c0510ca4bc4edd4cd895f315b7484bd81a0b21128a126bb337</t>
+          <t>0xadae1178f7a2de1bd568cf92b516d13b8fb88e70b856c02eb77c9e0b06e5b264</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4746,39 +4770,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>24.24999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -4786,7 +4810,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4816,7 +4840,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786689321</t>
+          <t>1786691887</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4826,7 +4850,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>31.089731</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,12 +4867,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x7da7c48dd0bea2c1605d7d5ab0f93d62934e030e84cc235f49d8042236775008</t>
+          <t>0x059b37e47835b5b6655b7816df8fe7ad06a8d6b06ae81642936f5913e3911b0e</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4858,39 +4882,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>Galatasaray SK -1.5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -4898,7 +4922,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4928,7 +4952,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786689255</t>
+          <t>1786691585</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4938,7 +4962,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4955,54 +4979,46 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x4a1609db924dd9c387fb8de9d105ed43baf4e58779d9aee234732e8e5e46518a</t>
+          <t>0x96a718e5036292c04eda8a099fc1bfe4931d68c324d251bc9680ac7dfae26c0d</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5010,7 +5026,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5040,7 +5056,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786689190</t>
+          <t>1786689484</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5050,7 +5066,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>5.856354</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5067,54 +5083,46 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xe00b9517350e97755646b6ef93ecbd8afec44689bc621cbc505841d25f40dca6</t>
+          <t>0xf3cb76ff35f741457025f079043311ce165e8adc8117fc4f8c39060ec00fe661</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5122,7 +5130,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5152,7 +5160,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786689123</t>
+          <t>1786689481</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5162,7 +5170,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>6.430939</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5179,54 +5187,46 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xc0332b54f5b348e9daf479d415fa4737f402ed9d6df41f0bb64b200f5841519f</t>
+          <t>0x1fa7a45b07827b4542762a5ca9e4abd3c2873b4e392b21dd381c3e57d08d393e</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>5.17999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786688930</t>
+          <t>1786689393</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>7.716931</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,31 +5291,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x9813458723b7b9d5f1364b30b7946d7873cfa8da02d134dbe51c5aec9d8812b2</t>
+          <t>0xc3edc7001ce622a365c9f22b4b276dcb3fa943b0e7eb37fbd16932024736a22d</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -5338,7 +5346,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5368,7 +5376,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786687874</t>
+          <t>1786689386</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5378,7 +5386,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>8.923944</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5395,12 +5403,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xb9bb9d24faf4bfd886f280157336237743d1d597ba75c92bea7de28848f20fb8</t>
+          <t>0x0277aa07615635c0510ca4bc4edd4cd895f315b7484bd81a0b21128a126bb337</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5410,22 +5418,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Galatasaray SK -2.5</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5450,7 +5458,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5480,7 +5488,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786687241</t>
+          <t>1786689321</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5490,7 +5498,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>41.594306</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5507,31 +5515,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xdc40bf9bc16cf235537e7a69812970c27c7cdf0ec057a88e8f2cdf05e633faf2</t>
+          <t>0x7da7c48dd0bea2c1605d7d5ab0f93d62934e030e84cc235f49d8042236775008</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -5554,7 +5570,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5584,7 +5600,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786685826</t>
+          <t>1786689255</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5594,7 +5610,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>48.959233</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5611,31 +5627,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
+          <t>0x4a1609db924dd9c387fb8de9d105ed43baf4e58779d9aee234732e8e5e46518a</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -5658,7 +5682,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5688,7 +5712,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786656294</t>
+          <t>1786689190</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5698,7 +5722,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2.31746</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5715,12 +5739,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
+          <t>0xe00b9517350e97755646b6ef93ecbd8afec44689bc621cbc505841d25f40dca6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5730,22 +5754,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5770,7 +5794,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5800,7 +5824,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786648026</t>
+          <t>1786689123</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5810,7 +5834,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>46.256716</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5827,12 +5851,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
+          <t>0xc0332b54f5b348e9daf479d415fa4737f402ed9d6df41f0bb64b200f5841519f</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5842,22 +5866,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20.5068</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4225</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5882,7 +5906,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5912,7 +5936,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786647838</t>
+          <t>1786688930</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5922,7 +5946,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>48.536805</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5939,39 +5963,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
+          <t>0x9813458723b7b9d5f1364b30b7946d7873cfa8da02d134dbe51c5aec9d8812b2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -5994,7 +6010,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6024,7 +6040,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786687874</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6034,7 +6050,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>47.619048</t>
+          <t>8.923944</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6051,12 +6067,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
+          <t>0xb9bb9d24faf4bfd886f280157336237743d1d597ba75c92bea7de28848f20fb8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6066,22 +6082,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Galatasaray SK -2.5</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6106,7 +6122,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6136,7 +6152,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786687241</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6146,7 +6162,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>47.595506</t>
+          <t>41.594306</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6163,28 +6179,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
+          <t>0xdc40bf9bc16cf235537e7a69812970c27c7cdf0ec057a88e8f2cdf05e633faf2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>38.62999</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6210,7 +6226,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6240,7 +6256,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786685826</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6250,7 +6266,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>47.617861</t>
+          <t>48.959233</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6267,7 +6283,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6278,12 +6294,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6344,7 +6360,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786647056</t>
+          <t>1786656294</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6354,7 +6370,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2.954092</t>
+          <t>2.31746</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6371,31 +6387,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>36.63999</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -6418,7 +6442,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6448,7 +6472,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786647056</t>
+          <t>1786648026</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6458,7 +6482,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>47.584403</t>
+          <t>46.256716</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6475,31 +6499,39 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>38.56999</t>
+          <t>20.5068</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.4225</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -6522,7 +6554,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6552,7 +6584,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786647838</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6562,7 +6594,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>47.617272</t>
+          <t>48.536805</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6579,7 +6611,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6594,22 +6626,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.1838</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-3.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Galatasaray SK -3.5</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6634,7 +6666,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6664,7 +6696,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786647057</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6674,7 +6706,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>47.595506</t>
+          <t>47.619048</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6691,7 +6723,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6706,22 +6738,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3.5</t>
+          <t>Galatasaray SK -3</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6746,7 +6778,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6776,7 +6808,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786647057</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6786,7 +6818,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>47.619048</t>
+          <t>47.595506</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6803,7 +6835,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6814,17 +6846,17 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>36.63999</t>
+          <t>38.62999</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-3.5)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6850,7 +6882,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6880,7 +6912,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786647057</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6890,7 +6922,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>47.584403</t>
+          <t>47.617861</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6907,110 +6939,750 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.6262</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2.954092</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>38.56999</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>47.617272</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>47.595506</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.1838</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3.5</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>47.619048</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>0x11d9d432d7e4905e6b4dea8d4ffd97ac3083c3474849e0f633bdb38cfe98e826</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>46.36</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Super Lig</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>L19547664</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>1786562478</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>1786732200</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>386.333333</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Super Lig/trades.xlsx
+++ b/data/sxbet/ligas/Super Lig/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:V73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd4e6c403ea408b2339c0602c38d8d658ec27335338ae119d72db90402419ab7f</t>
+          <t>0x7fb1dc037579f7ba4d00b2a528726cddba0b39831b675ffe115ac401510381b9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.49949</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1738</t>
+          <t>1.3962</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786711291</t>
+          <t>1786716094</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20.14095</t>
+          <t>17.337539</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xb11371348313ba14af90748e92e8584e7206b88a586c8c456c008804fe3d92e2</t>
+          <t>0xdb3955ab64e84eec71d615dcea3835b6766c966b42718d095514bc3139497a71</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.34126</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.1738</t>
+          <t>1.3025</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Galatasaray SK -2.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786711231</t>
+          <t>1786716093</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>27.798561</t>
+          <t>14.351273</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xa89cf31f8f686a1eb3d2d3b9e5dc11864cee90f422fb1e645205110d3f063f9e</t>
+          <t>0x1ba08e22321e823f20c9b41958dbe95c80c7e8e0376a1835b99f9d7e51da8da5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.83999</t>
+          <t>2.44033</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.665</t>
+          <t>1.2612</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galatasaray SK -1</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
+          <t>0x56384e65562fd972f39899236a327824c38df68371528d1ba26c12ba53c10218</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786710007</t>
+          <t>1786716093</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>7.27818</t>
+          <t>9.340976</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xee3ae1e73db70bebda3eed568a596a69fc4861c78488eb47519907204bd91476</t>
+          <t>0x29ed919650487b0f10d389ae1baf41c28b411b83fcb1034eed31660a56a605bd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -882,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36.82998</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.665</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galatasaray SK -1</t>
+          <t>Galatasaray SK -0.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786710005</t>
+          <t>1786713745</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>15.037594</t>
+          <t>49.519301</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x27e9f22b3d6dc53e4afcb141880f34ad08460246598c5e33ddc37551b5a494fb</t>
+          <t>0xab84a2d20d1ffd5dc3a2af33c8f4d1c0c58e0e6aea0203ffec7062cb2e2178ff</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -994,22 +994,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.13999</t>
+          <t>36.73573</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.665</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Galatasaray SK -1</t>
+          <t>Galatasaray SK -0.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786709961</t>
+          <t>1786713703</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>19.759383</t>
+          <t>49.475731</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,12 +1091,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x14d550541329b80b032170bb8cce7aeb98cd14feb66a15d56a7957278fc7559f</t>
+          <t>0x1ac314bb329ce90712e666060a1aeb5abd5307bc930f881d81b45e6cff97a546</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1106,22 +1106,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>36.82998</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5175</t>
+          <t>1.7437</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Galatasaray SK -1.5</t>
+          <t>Galatasaray SK -0.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786709961</t>
+          <t>1786713679</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>38.086957</t>
+          <t>49.519301</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x8eb95e07727eecff26d7e28ae9747c2ab7965a974c4dc6b1f0cf4f60fe3dcf67</t>
+          <t>0xd4e6c403ea408b2339c0602c38d8d658ec27335338ae119d72db90402419ab7f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1211,23 +1211,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.49949</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.1738</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1250,7 +1258,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1280,7 +1288,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786708704</t>
+          <t>1786711291</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1298,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20.100503</t>
+          <t>20.14095</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1315,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6d827309844d7af10e2fc666df00cec34b49d3535b88c1ad2d294e86742d5401</t>
+          <t>0xb11371348313ba14af90748e92e8584e7206b88a586c8c456c008804fe3d92e2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,22 +1330,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5175</t>
+          <t>1.1738</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galatasaray SK -1.5</t>
+          <t>Galatasaray SK -3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1362,7 +1370,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1392,7 +1400,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786708324</t>
+          <t>1786711231</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1402,7 +1410,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>11.033816</t>
+          <t>27.798561</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,7 +1427,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xdb1af061082debc5d686e26e1feeabf13afaf4c7367b6298b61ba4d7b393089d</t>
+          <t>0xa89cf31f8f686a1eb3d2d3b9e5dc11864cee90f422fb1e645205110d3f063f9e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1434,22 +1442,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.27497</t>
+          <t>4.83999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Galatasaray SK -0.5</t>
+          <t>Galatasaray SK -1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1474,7 +1482,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1504,7 +1512,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786707724</t>
+          <t>1786710007</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1514,7 +1522,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.717131</t>
+          <t>7.27818</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,7 +1539,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x3a1405dad01a1e2e879928f27e93a0b5953a34d0ab186c27c1b344a9592c19af</t>
+          <t>0xee3ae1e73db70bebda3eed568a596a69fc4861c78488eb47519907204bd91476</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,22 +1554,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27.55999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Galatasaray SK -0.5</t>
+          <t>Galatasaray SK -1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1586,7 +1594,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1616,7 +1624,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786707646</t>
+          <t>1786710005</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1626,7 +1634,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37.117832</t>
+          <t>15.037594</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,31 +1651,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xcaace36699e174f73e4672a10507967b8a93347b2a58f4ffdd1085b144145abc</t>
+          <t>0x27e9f22b3d6dc53e4afcb141880f34ad08460246598c5e33ddc37551b5a494fb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13.13999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1690,7 +1706,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1720,7 +1736,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786707458</t>
+          <t>1786709961</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1730,7 +1746,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.846154</t>
+          <t>19.759383</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,7 +1763,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x845eed293c0a679a4d7f44f97bfe24dc6873d8c15ecea6311e6f943f82806c2a</t>
+          <t>0x14d550541329b80b032170bb8cce7aeb98cd14feb66a15d56a7957278fc7559f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1762,22 +1778,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Galatasaray SK -1.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1802,7 +1818,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1832,7 +1848,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786707147</t>
+          <t>1786709961</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1842,7 +1858,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>151.240876</t>
+          <t>38.086957</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,7 +1875,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x773ca279dd1fcdfd95641d3e865ac1c15cfaf639cb57dcd1a5ce2b159a79d5c9</t>
+          <t>0x8eb95e07727eecff26d7e28ae9747c2ab7965a974c4dc6b1f0cf4f60fe3dcf67</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1867,31 +1883,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27.29998</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -1914,7 +1922,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1944,7 +1952,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786707081</t>
+          <t>1786708704</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1954,7 +1962,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36.76765</t>
+          <t>20.100503</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,31 +1979,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x7915c5da57ffdd5446ae88ee7510bd59159ace42a0d790506fe27eeccdfdd8e2</t>
+          <t>0x6d827309844d7af10e2fc666df00cec34b49d3535b88c1ad2d294e86742d5401</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>166.89</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2018,7 +2034,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2048,7 +2064,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786706610</t>
+          <t>1786708324</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2058,7 +2074,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>641.884615</t>
+          <t>11.033816</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,7 +2091,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x0a8fffbc18f527c688873f2f70c21af596b8a54395ec941e4feb87f4e916c50f</t>
+          <t>0xdb1af061082debc5d686e26e1feeabf13afaf4c7367b6298b61ba4d7b393089d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2083,15 +2099,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>1.27497</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2563</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2099,7 +2119,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2152,7 +2176,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786706610</t>
+          <t>1786707724</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2162,7 +2186,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>49.326829</t>
+          <t>1.717131</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,7 +2203,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xe495787704c21d9862422d18967d34d2427d09b118c7153251d21f8a358df4e3</t>
+          <t>0x3a1405dad01a1e2e879928f27e93a0b5953a34d0ab186c27c1b344a9592c19af</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2194,39 +2218,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>98.77998</t>
+          <t>27.55999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -2234,7 +2258,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2264,7 +2288,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786706354</t>
+          <t>1786707646</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2274,7 +2298,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>130.834411</t>
+          <t>37.117832</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,27 +2315,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x2f1937327bedbf2e7c212ccf58443b354ccd9877b2268e90e7e7db999d0c5634</t>
+          <t>0xcaace36699e174f73e4672a10507967b8a93347b2a58f4ffdd1085b144145abc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.32999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2319,26 +2339,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -2376,7 +2392,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786705734</t>
+          <t>1786707458</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2386,7 +2402,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>8.384093</t>
+          <t>3.846154</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,12 +2419,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x8c40f4ea25a8d84fec1a9f2051d284621eb317f39ef576e6259f3d3465e01764</t>
+          <t>0x845eed293c0a679a4d7f44f97bfe24dc6873d8c15ecea6311e6f943f82806c2a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2418,12 +2434,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13.47999</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2433,24 +2449,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -2458,7 +2474,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2488,7 +2504,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786705716</t>
+          <t>1786707147</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2498,7 +2514,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>17.854291</t>
+          <t>151.240876</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2515,7 +2531,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x0277dd0aebe5d8c7a8c9d9213d27aeb8863ee0b6dd6f25c9bc5c6cb8f8576da5</t>
+          <t>0x773ca279dd1fcdfd95641d3e865ac1c15cfaf639cb57dcd1a5ce2b159a79d5c9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,39 +2546,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>98.97998</t>
+          <t>27.29998</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -2570,7 +2586,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2600,7 +2616,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786705696</t>
+          <t>1786707081</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2610,7 +2626,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>131.099311</t>
+          <t>36.76765</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2627,7 +2643,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x46b66c2899b85f503cccc5f67de585ac56c4acbda40d70960ffad512c8e056e9</t>
+          <t>0x7915c5da57ffdd5446ae88ee7510bd59159ace42a0d790506fe27eeccdfdd8e2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2638,12 +2654,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>581.29412</t>
+          <t>166.89</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2674,7 +2690,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2704,7 +2720,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786704867</t>
+          <t>1786706610</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2714,7 +2730,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>635.29412</t>
+          <t>641.884615</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,7 +2747,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x4294e00d7858123ad3b26cdb24ecc9a518c262a27fdb5040280e0c1e04c58677</t>
+          <t>0x0a8fffbc18f527c688873f2f70c21af596b8a54395ec941e4feb87f4e916c50f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2742,17 +2758,17 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>602.81998</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1.2563</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2778,7 +2794,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2808,7 +2824,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786704864</t>
+          <t>1786706610</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2818,7 +2834,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>658.81965</t>
+          <t>49.326829</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2835,7 +2851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x4cf922d1e2d6269e67d6a514a4515188832fe859e91505d33649905388468d4f</t>
+          <t>0xe495787704c21d9862422d18967d34d2427d09b118c7153251d21f8a358df4e3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2843,23 +2859,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9.08999</t>
+          <t>98.77998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -2882,7 +2906,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2912,7 +2936,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786704852</t>
+          <t>1786706354</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2922,7 +2946,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>14.720632</t>
+          <t>130.834411</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2939,7 +2963,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x4d90e057d93cfc68db9ab18a085695bf869d7741bae368bdf2dbd877a68c2e20</t>
+          <t>0x2f1937327bedbf2e7c212ccf58443b354ccd9877b2268e90e7e7db999d0c5634</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2954,12 +2978,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>6.32999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2969,7 +2993,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2994,7 +3018,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3024,7 +3048,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786704038</t>
+          <t>1786705734</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3034,7 +3058,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>8.384093</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3051,7 +3075,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x5c7c7a69c35b22274ba0ee9ba3c275387e27cf9fae03a224b6537c798684b62e</t>
+          <t>0x8c40f4ea25a8d84fec1a9f2051d284621eb317f39ef576e6259f3d3465e01764</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3066,12 +3090,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>13.47999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3081,7 +3105,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3106,7 +3130,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3136,7 +3160,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786703866</t>
+          <t>1786705716</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3146,7 +3170,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>112.848485</t>
+          <t>17.854291</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3163,7 +3187,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x948dae997d9eccf400ee187c8ba958553204eae0142fe7a03cfae8cd6620e88f</t>
+          <t>0x0277dd0aebe5d8c7a8c9d9213d27aeb8863ee0b6dd6f25c9bc5c6cb8f8576da5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3178,22 +3202,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16.87999</t>
+          <t>98.97998</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6887</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Galatasaray SK -1</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3218,7 +3242,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3248,7 +3272,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786703243</t>
+          <t>1786705696</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3258,7 +3282,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>24.508152</t>
+          <t>131.099311</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3275,7 +3299,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x14663cbc9f1993a9a1da764fd8ce40f9e6844722ad5feb3ac8ead29430186a11</t>
+          <t>0x46b66c2899b85f503cccc5f67de585ac56c4acbda40d70960ffad512c8e056e9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3286,12 +3310,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>75.05993</t>
+          <t>581.29412</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.915</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3352,7 +3376,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786702892</t>
+          <t>1786704867</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3362,7 +3386,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>81.58688</t>
+          <t>635.29412</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3379,7 +3403,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xa1aab820d38249671bcf7e90f5586cda87617cdde2ee0be038153fc5954cdf7c</t>
+          <t>0x4294e00d7858123ad3b26cdb24ecc9a518c262a27fdb5040280e0c1e04c58677</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3390,12 +3414,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.42993</t>
+          <t>602.81998</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.9225</t>
+          <t>1.915</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3456,7 +3480,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786702195</t>
+          <t>1786704864</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3466,7 +3490,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2.63407</t>
+          <t>658.81965</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,39 +3507,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x600540942837eb33d421c900b7288a86c980a0b346f74dc131b7cdaa2dd6a496</t>
+          <t>0x4cf922d1e2d6269e67d6a514a4515188832fe859e91505d33649905388468d4f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.58999</t>
+          <t>9.08999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (2.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Genclerbirligi Sk +2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -3523,27 +3539,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Genclerbirligi Sk vs Fenerbahçe</t>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Genclerbirligi Sk</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xa72b64b0ca933e5c6954ea5a6c80db4ec664dc64836b150cc73917145232017c</t>
+          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19547685</t>
+          <t>L19547664</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3568,17 +3584,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786700733</t>
+          <t>1786704852</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786818600</t>
+          <t>1786732200</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>11.155831</t>
+          <t>14.720632</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3595,7 +3611,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x94d8e5004e7176f2726a9cc2be60d8e8fe8c164fafefddb52d96b40e5906351b</t>
+          <t>0x4d90e057d93cfc68db9ab18a085695bf869d7741bae368bdf2dbd877a68c2e20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3603,23 +3619,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10.39932</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -3642,7 +3666,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3672,7 +3696,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786697405</t>
+          <t>1786704038</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3682,7 +3706,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48.089341</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,7 +3723,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x057dfb059d29bb8e6462d635b019e406205008ed333601856f3a4f218c6e771a</t>
+          <t>0x5c7c7a69c35b22274ba0ee9ba3c275387e27cf9fae03a224b6537c798684b62e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3707,23 +3731,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10.39932</t>
+          <t>18.62</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -3746,7 +3778,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3776,7 +3808,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786697375</t>
+          <t>1786703866</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3786,7 +3818,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>48.089341</t>
+          <t>112.848485</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,7 +3835,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x6427f3d101c0e917aac28af7ae32d70fd3726361b8179434942b0d430ef7462e</t>
+          <t>0x948dae997d9eccf400ee187c8ba958553204eae0142fe7a03cfae8cd6620e88f</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3811,23 +3843,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10.39932</t>
+          <t>16.87999</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.6887</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -1</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -3850,7 +3890,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+          <t>0x401464d4db823dbd8b5e31c2fed272e9f7dd67f411f6a1e9f1e1ab3e75d56666</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3880,7 +3920,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786697304</t>
+          <t>1786703243</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3890,7 +3930,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>48.089341</t>
+          <t>24.508152</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3907,7 +3947,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x911930dbac03eadd0379cbbe8ce10fe735e42e19c463219a6faa55e601aeb785</t>
+          <t>0x14663cbc9f1993a9a1da764fd8ce40f9e6844722ad5feb3ac8ead29430186a11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3918,17 +3958,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>75.05993</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3954,7 +3994,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
+          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3984,7 +4024,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786697101</t>
+          <t>1786702892</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3994,7 +4034,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>17.433526</t>
+          <t>81.58688</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4011,23 +4051,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xaac60d693bf0fa6ec90126590d2cd2187f392b62165508184f545018e85eb9c3</t>
+          <t>0xa1aab820d38249671bcf7e90f5586cda87617cdde2ee0be038153fc5954cdf7c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>2.42993</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.9225</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4058,7 +4098,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xfc4d71ba8539517d0b42d9e30db07f56eee12bb466f34b9b938f1955ca32a505</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4088,7 +4128,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786695468</t>
+          <t>1786702195</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4098,7 +4138,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>2.63407</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4115,31 +4155,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xb6078a9dbff76d9a3d0fd7dfc6fa4e942f2e57ee6fed05cbe866739451772a61</t>
+          <t>0x600540942837eb33d421c900b7288a86c980a0b346f74dc131b7cdaa2dd6a496</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>8.58999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Asian Handicap (2.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Genclerbirligi Sk +2.5</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4147,27 +4195,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
+          <t>Genclerbirligi Sk vs Fenerbahçe</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Galatasaray SK</t>
+          <t>Genclerbirligi Sk</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xa72b64b0ca933e5c6954ea5a6c80db4ec664dc64836b150cc73917145232017c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19547664</t>
+          <t>L19547685</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4192,17 +4240,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786695402</t>
+          <t>1786700733</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786732200</t>
+          <t>1786818600</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>11.155831</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4219,28 +4267,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xd7d25e989c7c1bd73d8577425cd04cb6e99a4d9ea63e81d66a1cb585735b1074</t>
+          <t>0x94d8e5004e7176f2726a9cc2be60d8e8fe8c164fafefddb52d96b40e5906351b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>10.39932</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4266,7 +4314,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4296,7 +4344,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786695334</t>
+          <t>1786697405</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4306,7 +4354,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>48.089341</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4323,28 +4371,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x153e5d73875db805ab5926c57372cc9323e0210ac7d4b7771cb0a4d95b566bd4</t>
+          <t>0x057dfb059d29bb8e6462d635b019e406205008ed333601856f3a4f218c6e771a</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>10.39932</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4370,7 +4418,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4400,7 +4448,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786695268</t>
+          <t>1786697375</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4410,7 +4458,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>48.089341</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4427,28 +4475,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xe10683ef299398b0f5aa0bf3e8b236543904b1a2f82516e2445529aa80612887</t>
+          <t>0x6427f3d101c0e917aac28af7ae32d70fd3726361b8179434942b0d430ef7462e</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>49.99999</t>
+          <t>10.39932</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4474,7 +4522,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4504,7 +4552,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786695203</t>
+          <t>1786697304</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4514,7 +4562,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>58.224151</t>
+          <t>48.089341</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,39 +4579,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x484b9ddb00f67185222c5271ad11dc2e37e0c64fe540a5d49ad83c64a11b8b9b</t>
+          <t>0x911930dbac03eadd0379cbbe8ce10fe735e42e19c463219a6faa55e601aeb785</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.7625</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4571,27 +4611,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Torku Konyaspor vs Caykur Rizespor</t>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Torku Konyaspor</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Caykur Rizespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x0bba83fa89f6167caadeccbb2b3930657f0a248835be4ce38ba9a0e9ae3dbb78</t>
+          <t>0xf8f71416d0e8ba9190caf7101cc351fa6760c2bb5b7470509fb9680f1927f241</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19547688</t>
+          <t>L19547664</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4616,17 +4656,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786692830</t>
+          <t>1786697101</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786809600</t>
+          <t>1786732200</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>65.57377</t>
+          <t>17.433526</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4643,39 +4683,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x4a744a7164e08e94c9d15a1a5264ddd58945124df502dfc3b015e5af160a4432</t>
+          <t>0xaac60d693bf0fa6ec90126590d2cd2187f392b62165508184f545018e85eb9c3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.79998</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4698,7 +4730,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4728,7 +4760,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786691914</t>
+          <t>1786695468</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4738,7 +4770,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>17.692282</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4755,39 +4787,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xadae1178f7a2de1bd568cf92b516d13b8fb88e70b856c02eb77c9e0b06e5b264</t>
+          <t>0xb6078a9dbff76d9a3d0fd7dfc6fa4e942f2e57ee6fed05cbe866739451772a61</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>24.24999</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4810,7 +4834,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4840,7 +4864,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786691887</t>
+          <t>1786695402</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4850,7 +4874,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>31.089731</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,39 +4891,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x059b37e47835b5b6655b7816df8fe7ad06a8d6b06ae81642936f5913e3911b0e</t>
+          <t>0xd7d25e989c7c1bd73d8577425cd04cb6e99a4d9ea63e81d66a1cb585735b1074</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -4922,7 +4938,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4952,7 +4968,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786691585</t>
+          <t>1786695334</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4962,7 +4978,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4979,28 +4995,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x96a718e5036292c04eda8a099fc1bfe4931d68c324d251bc9680ac7dfae26c0d</t>
+          <t>0x153e5d73875db805ab5926c57372cc9323e0210ac7d4b7771cb0a4d95b566bd4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -5026,7 +5042,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5056,7 +5072,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786689484</t>
+          <t>1786695268</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5066,7 +5082,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>5.856354</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5083,28 +5099,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xf3cb76ff35f741457025f079043311ce165e8adc8117fc4f8c39060ec00fe661</t>
+          <t>0xe10683ef299398b0f5aa0bf3e8b236543904b1a2f82516e2445529aa80612887</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>49.99999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5130,7 +5146,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5160,7 +5176,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786689481</t>
+          <t>1786695203</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5170,7 +5186,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>6.430939</t>
+          <t>58.224151</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5187,31 +5203,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1fa7a45b07827b4542762a5ca9e4abd3c2873b4e392b21dd381c3e57d08d393e</t>
+          <t>0x484b9ddb00f67185222c5271ad11dc2e37e0c64fe540a5d49ad83c64a11b8b9b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5.17999</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.7625</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -5219,27 +5243,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
+          <t>Torku Konyaspor vs Caykur Rizespor</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Galatasaray SK</t>
+          <t>Torku Konyaspor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Caykur Rizespor</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x0bba83fa89f6167caadeccbb2b3930657f0a248835be4ce38ba9a0e9ae3dbb78</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19547664</t>
+          <t>L19547688</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5264,17 +5288,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786689393</t>
+          <t>1786692830</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786732200</t>
+          <t>1786809600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>7.716931</t>
+          <t>65.57377</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,12 +5315,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xc3edc7001ce622a365c9f22b4b276dcb3fa943b0e7eb37fbd16932024736a22d</t>
+          <t>0x4a744a7164e08e94c9d15a1a5264ddd58945124df502dfc3b015e5af160a4432</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5306,39 +5330,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>13.79998</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5346,7 +5370,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5376,7 +5400,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786689386</t>
+          <t>1786691914</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5386,7 +5410,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>17.692282</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5403,12 +5427,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x0277aa07615635c0510ca4bc4edd4cd895f315b7484bd81a0b21128a126bb337</t>
+          <t>0xadae1178f7a2de1bd568cf92b516d13b8fb88e70b856c02eb77c9e0b06e5b264</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5418,39 +5442,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>24.24999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>Galatasaray SK -0.5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5458,7 +5482,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0xf6b235aa31ceae72c18452c4dda82eded80bf2afed08ae907b8791a76ef36938</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5488,7 +5512,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786689321</t>
+          <t>1786691887</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5498,7 +5522,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>31.089731</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5515,12 +5539,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x7da7c48dd0bea2c1605d7d5ab0f93d62934e030e84cc235f49d8042236775008</t>
+          <t>0x059b37e47835b5b6655b7816df8fe7ad06a8d6b06ae81642936f5913e3911b0e</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5530,39 +5554,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>Galatasaray SK -1.5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5570,7 +5594,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5600,7 +5624,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786689255</t>
+          <t>1786691585</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5610,7 +5634,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5627,54 +5651,46 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x4a1609db924dd9c387fb8de9d105ed43baf4e58779d9aee234732e8e5e46518a</t>
+          <t>0x96a718e5036292c04eda8a099fc1bfe4931d68c324d251bc9680ac7dfae26c0d</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5682,7 +5698,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5712,7 +5728,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786689190</t>
+          <t>1786689484</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5722,7 +5738,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>5.856354</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5739,54 +5755,46 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xe00b9517350e97755646b6ef93ecbd8afec44689bc621cbc505841d25f40dca6</t>
+          <t>0xf3cb76ff35f741457025f079043311ce165e8adc8117fc4f8c39060ec00fe661</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5794,7 +5802,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5824,7 +5832,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786689123</t>
+          <t>1786689481</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5834,7 +5842,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>6.430939</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5851,54 +5859,46 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xc0332b54f5b348e9daf479d415fa4737f402ed9d6df41f0bb64b200f5841519f</t>
+          <t>0x1fa7a45b07827b4542762a5ca9e4abd3c2873b4e392b21dd381c3e57d08d393e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>49.99998</t>
+          <t>5.17999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Super Lig</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Galatasaray SK vs Çorum Belediyespor</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Galatasaray SK</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786688930</t>
+          <t>1786689393</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>62.992101</t>
+          <t>7.716931</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5963,31 +5963,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x9813458723b7b9d5f1364b30b7946d7873cfa8da02d134dbe51c5aec9d8812b2</t>
+          <t>0xc3edc7001ce622a365c9f22b4b276dcb3fa943b0e7eb37fbd16932024736a22d</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -6010,7 +6018,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6040,7 +6048,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786687874</t>
+          <t>1786689386</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6050,7 +6058,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>8.923944</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6067,12 +6075,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xb9bb9d24faf4bfd886f280157336237743d1d597ba75c92bea7de28848f20fb8</t>
+          <t>0x0277aa07615635c0510ca4bc4edd4cd895f315b7484bd81a0b21128a126bb337</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6082,22 +6090,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.3513</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Galatasaray SK -2.5</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6122,7 +6130,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6152,7 +6160,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786687241</t>
+          <t>1786689321</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6162,7 +6170,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>41.594306</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6179,31 +6187,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xdc40bf9bc16cf235537e7a69812970c27c7cdf0ec057a88e8f2cdf05e633faf2</t>
+          <t>0x7da7c48dd0bea2c1605d7d5ab0f93d62934e030e84cc235f49d8042236775008</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -6226,7 +6242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6256,7 +6272,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786685826</t>
+          <t>1786689255</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6266,7 +6282,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>48.959233</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6283,31 +6299,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
+          <t>0x4a1609db924dd9c387fb8de9d105ed43baf4e58779d9aee234732e8e5e46518a</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -6330,7 +6354,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6360,7 +6384,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786656294</t>
+          <t>1786689190</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6370,7 +6394,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2.31746</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6387,12 +6411,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
+          <t>0xe00b9517350e97755646b6ef93ecbd8afec44689bc621cbc505841d25f40dca6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6402,22 +6426,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19.37</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6442,7 +6466,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6472,7 +6496,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786648026</t>
+          <t>1786689123</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6482,7 +6506,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>46.256716</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6499,12 +6523,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
+          <t>0xc0332b54f5b348e9daf479d415fa4737f402ed9d6df41f0bb64b200f5841519f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x47d3E967E91199423245cDD504Db05a98BC30879</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6514,22 +6538,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20.5068</t>
+          <t>49.99998</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4225</t>
+          <t>1.7937</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Galatasaray SK</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6554,7 +6578,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
+          <t>0x97cd5bbd00a899486a9316ad3ba0202acc7287a902df48df686c3dfb99d2c87c</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6584,7 +6608,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786647838</t>
+          <t>1786688930</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6594,7 +6618,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>48.536805</t>
+          <t>62.992101</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6611,39 +6635,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
+          <t>0x9813458723b7b9d5f1364b30b7946d7873cfa8da02d134dbe51c5aec9d8812b2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Galatasaray SK -3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -6666,7 +6682,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x92a4b307c8651d305af4dfbd1e86ee9743b7e70d677a968b1408edf25a504ed2</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6696,7 +6712,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786687874</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6706,7 +6722,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>47.619048</t>
+          <t>8.923944</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6723,12 +6739,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
+          <t>0xb9bb9d24faf4bfd886f280157336237743d1d597ba75c92bea7de28848f20fb8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6738,22 +6754,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.3513</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Galatasaray SK -2.5</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6778,7 +6794,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6808,7 +6824,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786687241</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6818,7 +6834,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>47.595506</t>
+          <t>41.594306</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6835,28 +6851,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
+          <t>0xdc40bf9bc16cf235537e7a69812970c27c7cdf0ec057a88e8f2cdf05e633faf2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>38.62999</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6882,7 +6898,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x091a5ac34c3d849a0f627a5e65f99dd4577e707777eb7c09062a8efc5cc5e4a6</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6912,7 +6928,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786647057</t>
+          <t>1786685826</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6922,7 +6938,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>47.617861</t>
+          <t>48.959233</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6939,7 +6955,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+          <t>0x1b93f15de878604ef336b70df6f5e2973600cbf8bfd856dbf23aa94a5860905e</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6950,12 +6966,12 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.6262</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7016,7 +7032,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786647056</t>
+          <t>1786656294</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7026,7 +7042,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2.954092</t>
+          <t>2.31746</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7043,31 +7059,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+          <t>0x1d880eee8a237cf6377a3475271158d2cf700a619f83c9afe58edeca6183e590</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>36.63999</t>
+          <t>19.37</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -7090,7 +7114,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7120,7 +7144,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786647056</t>
+          <t>1786648026</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7130,7 +7154,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>47.584403</t>
+          <t>46.256716</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7147,31 +7171,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+          <t>0xbf9212ffbb0153c96812995cb25ecbbaca6652a2cb6a393f26568afd68454215</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>38.56999</t>
+          <t>20.5068</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.4225</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Super Lig</t>
@@ -7194,7 +7226,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x7e6cf23ba109d877a370614aaccb4dd7c8c3d1150b4b22b3c4f27baec2814504</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7224,7 +7256,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786647838</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7234,7 +7266,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>47.617272</t>
+          <t>48.536805</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7251,7 +7283,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+          <t>0xc871d8d8da812bc82099f934ba9e8cef14190ecca91102e1d122540de0c4a6f0</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7266,22 +7298,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.1838</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-3.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3</t>
+          <t>Galatasaray SK -3.5</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7306,7 +7338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7336,7 +7368,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786647057</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7346,7 +7378,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>47.595506</t>
+          <t>47.619048</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7363,7 +7395,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+          <t>0xb47dda0b0a8144c1d457593ffcc3baefcca2b6c4175886346c9ad42e060ddc71</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7378,22 +7410,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.1838</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Galatasaray SK -3.5</t>
+          <t>Galatasaray SK -3</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7418,7 +7450,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7448,7 +7480,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786647057</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7458,7 +7490,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>47.619048</t>
+          <t>47.595506</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7475,7 +7507,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+          <t>0x9fa1c4f1e854433138f75fe6f837be91e44ca6a01bfb448dc66f6d783245f100</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7486,17 +7518,17 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>36.63999</t>
+          <t>38.62999</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-3.5)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7522,7 +7554,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7552,7 +7584,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786647022</t>
+          <t>1786647057</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7562,7 +7594,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>47.584403</t>
+          <t>47.617861</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7579,110 +7611,750 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>0x915b6594ec3bf1ae7d8b7a9417d44198ba0e9b55470147a4dfe0ff0fa8fe8776</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.6262</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x00ecd526f15e3a0fa8e69eea49fcc98a63cda37be5b2aa54fffb7627bbdb11f9</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2.954092</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x09569a341d3f9d59d25e5956d6759160c0f4b49fcc5e37ca82d290aa9859dd03</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1786647056</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x5b42755a9658c59255c8e2296764fdcb8eb90963b9902f070f842148d3c2ca36</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>38.56999</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>47.617272</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x36cda961b50f1b9e21b19c25e5c990db1c29a72708fde0be8477efef760e6e5a</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.2225</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>47.595506</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x276dc93feb8df2fe7d411497bb628110f62eef81f9b91198a4cfa49959cccf8f</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.1838</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Galatasaray SK -3.5</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0xb4b2293ad53acee4f2edaa42f60d20000355c852afe5905db900bf288f3e9334</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>47.619048</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x047b60424d57ddf9de17a030740c7be12dfa68cff7fab704d639179e960a9781</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>36.63999</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Super Lig</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Galatasaray SK vs Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Galatasaray SK</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Çorum Belediyespor</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x011483e13ce2e8ce2dd3f2f8b8b16ca08cbe9dffb9e4bb560e81338f57636216</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19547664</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1786647022</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786732200</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>47.584403</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>0x11d9d432d7e4905e6b4dea8d4ffd97ac3083c3474849e0f633bdb38cfe98e826</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>46.36</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Super Lig</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Galatasaray SK vs Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Galatasaray SK</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Çorum Belediyespor</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>0x1318762019c8196916646db09feb952301c9ace396345d4d9a7823ce4ff4e756</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>L19547664</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>1786562478</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>1786732200</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>386.333333</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
